--- a/VanBanNoiBo/12.xlsx
+++ b/VanBanNoiBo/12.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>SỐ KÝ HIỆU</t>
   </si>
@@ -44,34 +44,67 @@
     <t>NỘI DUNG</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>hop dong nhan su</t>
+  </si>
+  <si>
+    <t>Bản vẽ</t>
+  </si>
+  <si>
+    <t>Ban Giám đốc</t>
+  </si>
+  <si>
+    <t>Phòng Kế hoạch</t>
+  </si>
+  <si>
+    <t>Quynh</t>
+  </si>
+  <si>
+    <t>Thao</t>
+  </si>
+  <si>
+    <t>Thuy</t>
+  </si>
+  <si>
+    <t>Coteccons</t>
+  </si>
+  <si>
+    <t>Hop dong 2023</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>hop dong nhan su</t>
-  </si>
-  <si>
-    <t>Bản vẽ</t>
-  </si>
-  <si>
-    <t>Ban Giám đốc</t>
-  </si>
-  <si>
-    <t>Phòng Kế hoạch</t>
-  </si>
-  <si>
-    <t>Quynh</t>
-  </si>
-  <si>
-    <t>Thao</t>
-  </si>
-  <si>
-    <t>Thuy</t>
-  </si>
-  <si>
-    <t>Coteccons</t>
-  </si>
-  <si>
-    <t>Hop dong 2023</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Văn bản số 1 </t>
+  </si>
+  <si>
+    <t>Hồ sơ dự án</t>
+  </si>
+  <si>
+    <t>Phòng Dự toán</t>
+  </si>
+  <si>
+    <t>Quốc Việt</t>
+  </si>
+  <si>
+    <t>Quỳnh</t>
+  </si>
+  <si>
+    <t>Thảo</t>
+  </si>
+  <si>
+    <t>Lý</t>
+  </si>
+  <si>
+    <t>Nội dung Coteccons</t>
   </si>
 </sst>
 </file>
@@ -131,7 +164,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -198,6 +231,102 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>
